--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/152.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/152.xlsx
@@ -426,13 +426,13 @@
         <v>-0.7376624587788279</v>
       </c>
       <c r="E2">
-        <v>-16.39041071328378</v>
+        <v>-17.4574278728671</v>
       </c>
       <c r="F2">
-        <v>3.06518041720721</v>
+        <v>3.610130196812893</v>
       </c>
       <c r="G2">
-        <v>-5.395644139666389</v>
+        <v>-7.754530326582063</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-0.4961938227313225</v>
       </c>
       <c r="E3">
-        <v>-17.38073363707319</v>
+        <v>-16.08354772910201</v>
       </c>
       <c r="F3">
-        <v>3.375796655704552</v>
+        <v>3.255426588403756</v>
       </c>
       <c r="G3">
-        <v>-5.050158917733587</v>
+        <v>-7.464476879158818</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-0.2357554682209911</v>
       </c>
       <c r="E4">
-        <v>-17.33924828668892</v>
+        <v>-16.60410940170574</v>
       </c>
       <c r="F4">
-        <v>3.209750409813391</v>
+        <v>3.861125519861143</v>
       </c>
       <c r="G4">
-        <v>-5.036195036648941</v>
+        <v>-7.57144060553267</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>0.02809529899420912</v>
       </c>
       <c r="E5">
-        <v>-18.81491946919843</v>
+        <v>-19.05624184906718</v>
       </c>
       <c r="F5">
-        <v>3.510613450510172</v>
+        <v>3.341843532598606</v>
       </c>
       <c r="G5">
-        <v>-5.05804794775367</v>
+        <v>-6.623595001638397</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>0.2962414690232164</v>
       </c>
       <c r="E6">
-        <v>-17.13408124329741</v>
+        <v>-19.26432070124562</v>
       </c>
       <c r="F6">
-        <v>3.194559808380854</v>
+        <v>4.042928970488356</v>
       </c>
       <c r="G6">
-        <v>-4.121216528868553</v>
+        <v>-6.770063467932372</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>0.5642260175327031</v>
       </c>
       <c r="E7">
-        <v>-19.06472820935755</v>
+        <v>-20.26326131107164</v>
       </c>
       <c r="F7">
-        <v>3.587416362628131</v>
+        <v>3.304452684771042</v>
       </c>
       <c r="G7">
-        <v>-4.3365807583803</v>
+        <v>-5.537567226934945</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>0.8311523420367296</v>
       </c>
       <c r="E8">
-        <v>-19.64019310083028</v>
+        <v>-19.54757675042541</v>
       </c>
       <c r="F8">
-        <v>3.771461375447319</v>
+        <v>3.783378268903993</v>
       </c>
       <c r="G8">
-        <v>-3.974201822560598</v>
+        <v>-5.488862480961187</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>1.091984499685209</v>
       </c>
       <c r="E9">
-        <v>-19.71875759638935</v>
+        <v>-20.09124269741627</v>
       </c>
       <c r="F9">
-        <v>3.560744588992792</v>
+        <v>4.091088594552314</v>
       </c>
       <c r="G9">
-        <v>-3.188827862097137</v>
+        <v>-5.318862656974073</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>1.347655501971127</v>
       </c>
       <c r="E10">
-        <v>-21.22389555926677</v>
+        <v>-22.11230517551356</v>
       </c>
       <c r="F10">
-        <v>3.534309728434654</v>
+        <v>4.467565011776633</v>
       </c>
       <c r="G10">
-        <v>-3.132323470832857</v>
+        <v>-4.38837093279666</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>1.598104701665979</v>
       </c>
       <c r="E11">
-        <v>-21.88965369397843</v>
+        <v>-21.68901059612058</v>
       </c>
       <c r="F11">
-        <v>3.987807746771272</v>
+        <v>4.345799973769523</v>
       </c>
       <c r="G11">
-        <v>-2.904134187901972</v>
+        <v>-3.58250469544511</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.845220050987603</v>
       </c>
       <c r="E12">
-        <v>-22.19494076920553</v>
+        <v>-21.8996163367953</v>
       </c>
       <c r="F12">
-        <v>4.321714363165724</v>
+        <v>4.796128658423029</v>
       </c>
       <c r="G12">
-        <v>-3.538636656504227</v>
+        <v>-3.360578964674526</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.091212069888289</v>
       </c>
       <c r="E13">
-        <v>-22.56793305932131</v>
+        <v>-23.00777921121232</v>
       </c>
       <c r="F13">
-        <v>4.630312698669846</v>
+        <v>4.573417111975965</v>
       </c>
       <c r="G13">
-        <v>-2.860332359871875</v>
+        <v>-3.154676274314016</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.335991869084582</v>
       </c>
       <c r="E14">
-        <v>-24.37130273492186</v>
+        <v>-24.36418850225581</v>
       </c>
       <c r="F14">
-        <v>4.830628504014824</v>
+        <v>5.108539140714835</v>
       </c>
       <c r="G14">
-        <v>-2.292110323511368</v>
+        <v>-2.835675416695383</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.581531965454062</v>
       </c>
       <c r="E15">
-        <v>-23.32119942575719</v>
+        <v>-24.95300333510315</v>
       </c>
       <c r="F15">
-        <v>4.935039244933284</v>
+        <v>4.994670100791209</v>
       </c>
       <c r="G15">
-        <v>-1.453800739874962</v>
+        <v>-3.288134296638655</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.829491792092728</v>
       </c>
       <c r="E16">
-        <v>-24.03158114334044</v>
+        <v>-25.72148990267882</v>
       </c>
       <c r="F16">
-        <v>4.986825461486698</v>
+        <v>5.283975759484131</v>
       </c>
       <c r="G16">
-        <v>-1.826492025049494</v>
+        <v>-2.711251873147415</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.079958187591593</v>
       </c>
       <c r="E17">
-        <v>-25.34287324784551</v>
+        <v>-26.313166731099</v>
       </c>
       <c r="F17">
-        <v>5.767568365564454</v>
+        <v>5.557385047717331</v>
       </c>
       <c r="G17">
-        <v>-1.479560094716031</v>
+        <v>-1.858690390964445</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.331879190764067</v>
       </c>
       <c r="E18">
-        <v>-27.33940498224325</v>
+        <v>-25.52176155657052</v>
       </c>
       <c r="F18">
-        <v>5.070170819351968</v>
+        <v>5.942703458599132</v>
       </c>
       <c r="G18">
-        <v>-1.097708530034335</v>
+        <v>-1.605003286290094</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.582814326586968</v>
       </c>
       <c r="E19">
-        <v>-27.78171009552043</v>
+        <v>-28.29950939897948</v>
       </c>
       <c r="F19">
-        <v>5.570494790234036</v>
+        <v>6.212295629840231</v>
       </c>
       <c r="G19">
-        <v>-1.708020842381135</v>
+        <v>-2.160545933235192</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.829523521453301</v>
       </c>
       <c r="E20">
-        <v>-27.84673445379657</v>
+        <v>-26.98668667025981</v>
       </c>
       <c r="F20">
-        <v>6.386017528085731</v>
+        <v>6.611157847757804</v>
       </c>
       <c r="G20">
-        <v>-0.7102687644823493</v>
+        <v>-1.428892195237485</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.070967061543548</v>
       </c>
       <c r="E21">
-        <v>-28.260849816376</v>
+        <v>-29.0276427346728</v>
       </c>
       <c r="F21">
-        <v>6.138473183637545</v>
+        <v>7.05111537252826</v>
       </c>
       <c r="G21">
-        <v>0.05042838953138408</v>
+        <v>-1.390781194989395</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.303930925966791</v>
       </c>
       <c r="E22">
-        <v>-28.12987729112616</v>
+        <v>-28.32532170082321</v>
       </c>
       <c r="F22">
-        <v>6.44224048044854</v>
+        <v>6.954698377046815</v>
       </c>
       <c r="G22">
-        <v>-1.054347004560961</v>
+        <v>-1.813445165079226</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.523736638192863</v>
       </c>
       <c r="E23">
-        <v>-29.17547929712721</v>
+        <v>-29.72087059271499</v>
       </c>
       <c r="F23">
-        <v>6.512953235421117</v>
+        <v>6.74758333205966</v>
       </c>
       <c r="G23">
-        <v>-0.3823592288175382</v>
+        <v>-1.334194040086633</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.724971541815226</v>
       </c>
       <c r="E24">
-        <v>-28.62437306734174</v>
+        <v>-29.44202980569269</v>
       </c>
       <c r="F24">
-        <v>7.269312316630067</v>
+        <v>7.093542694164846</v>
       </c>
       <c r="G24">
-        <v>-1.658663918936141</v>
+        <v>-1.004318040371495</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.900011212147231</v>
       </c>
       <c r="E25">
-        <v>-29.55429067634284</v>
+        <v>-28.89847707055202</v>
       </c>
       <c r="F25">
-        <v>7.03575247067594</v>
+        <v>7.220456863947757</v>
       </c>
       <c r="G25">
-        <v>-0.09197803738590531</v>
+        <v>-1.621734783445571</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.045050086586068</v>
       </c>
       <c r="E26">
-        <v>-29.88934567545936</v>
+        <v>-30.20131451408477</v>
       </c>
       <c r="F26">
-        <v>6.757177483318884</v>
+        <v>6.698659953250321</v>
       </c>
       <c r="G26">
-        <v>-0.6039141784877231</v>
+        <v>-1.532836704079522</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.155354002288456</v>
       </c>
       <c r="E27">
-        <v>-29.40386382675604</v>
+        <v>-29.55586658529751</v>
       </c>
       <c r="F27">
-        <v>7.140120136489456</v>
+        <v>6.916427803037478</v>
       </c>
       <c r="G27">
-        <v>-0.5589801438831953</v>
+        <v>-1.423883339836568</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.228008125104977</v>
       </c>
       <c r="E28">
-        <v>-30.31327650545041</v>
+        <v>-29.52293325807673</v>
       </c>
       <c r="F28">
-        <v>6.799308249425267</v>
+        <v>6.648641472734481</v>
       </c>
       <c r="G28">
-        <v>-0.9889008297951087</v>
+        <v>-0.9117783609122472</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.261716770005379</v>
       </c>
       <c r="E29">
-        <v>-30.09378137029863</v>
+        <v>-30.64241505327591</v>
       </c>
       <c r="F29">
-        <v>6.911053355328114</v>
+        <v>6.966338595790954</v>
       </c>
       <c r="G29">
-        <v>-1.075729818199114</v>
+        <v>-1.286571842504217</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.259011988238876</v>
       </c>
       <c r="E30">
-        <v>-29.00790311647336</v>
+        <v>-30.19563580767915</v>
       </c>
       <c r="F30">
-        <v>6.737727416701151</v>
+        <v>7.013240758137462</v>
       </c>
       <c r="G30">
-        <v>-1.410598120587472</v>
+        <v>-0.9496543124270488</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.226189677784538</v>
       </c>
       <c r="E31">
-        <v>-28.94560942802385</v>
+        <v>-29.76785124630757</v>
       </c>
       <c r="F31">
-        <v>6.542835761109706</v>
+        <v>7.031902218987729</v>
       </c>
       <c r="G31">
-        <v>-1.315671537794411</v>
+        <v>-2.396458718909197</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.17118209453792</v>
       </c>
       <c r="E32">
-        <v>-28.73480443449279</v>
+        <v>-29.2199307979865</v>
       </c>
       <c r="F32">
-        <v>7.111922510098161</v>
+        <v>6.592014277079107</v>
       </c>
       <c r="G32">
-        <v>-0.6644110876723648</v>
+        <v>-1.898029603607605</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.102230356352335</v>
       </c>
       <c r="E33">
-        <v>-28.36327031300748</v>
+        <v>-29.98786262749623</v>
       </c>
       <c r="F33">
-        <v>6.313565201567275</v>
+        <v>6.772666297016429</v>
       </c>
       <c r="G33">
-        <v>-0.3847097161504208</v>
+        <v>-1.337365542713255</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>5.025753165315854</v>
       </c>
       <c r="E34">
-        <v>-28.59974722568803</v>
+        <v>-28.79687169924192</v>
       </c>
       <c r="F34">
-        <v>6.923871512519034</v>
+        <v>6.607938812030524</v>
       </c>
       <c r="G34">
-        <v>-2.144407023731245</v>
+        <v>-1.594250634378542</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>4.948726705463006</v>
       </c>
       <c r="E35">
-        <v>-27.28456063353636</v>
+        <v>-28.32843729094048</v>
       </c>
       <c r="F35">
-        <v>6.313508872583886</v>
+        <v>6.540940456492101</v>
       </c>
       <c r="G35">
-        <v>-2.171659434610526</v>
+        <v>-2.260137074693088</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>4.875030435291561</v>
       </c>
       <c r="E36">
-        <v>-28.06846665510814</v>
+        <v>-28.21459145438765</v>
       </c>
       <c r="F36">
-        <v>6.385629852141221</v>
+        <v>6.36867151467111</v>
       </c>
       <c r="G36">
-        <v>-2.101859892460532</v>
+        <v>-1.734813087430457</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>4.807134283570796</v>
       </c>
       <c r="E37">
-        <v>-27.83918095915178</v>
+        <v>-28.31979243405984</v>
       </c>
       <c r="F37">
-        <v>6.552010758463114</v>
+        <v>6.58864779195413</v>
       </c>
       <c r="G37">
-        <v>-1.916446168442571</v>
+        <v>-1.822294253305698</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>4.74423537038727</v>
       </c>
       <c r="E38">
-        <v>-27.08355525775789</v>
+        <v>-26.61065124561089</v>
       </c>
       <c r="F38">
-        <v>6.379165272929774</v>
+        <v>6.12796451476563</v>
       </c>
       <c r="G38">
-        <v>-2.413329258977322</v>
+        <v>-1.454687966079486</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>4.682955239724333</v>
       </c>
       <c r="E39">
-        <v>-26.24854993548356</v>
+        <v>-27.36254095594844</v>
       </c>
       <c r="F39">
-        <v>6.66210741323439</v>
+        <v>6.527161393113934</v>
       </c>
       <c r="G39">
-        <v>-0.8997908755145462</v>
+        <v>-1.648381364491165</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>4.620429710508345</v>
       </c>
       <c r="E40">
-        <v>-25.25342682924601</v>
+        <v>-26.68041691617305</v>
       </c>
       <c r="F40">
-        <v>6.628382919531616</v>
+        <v>6.569454519231265</v>
       </c>
       <c r="G40">
-        <v>-1.2196028167903</v>
+        <v>-2.385034026253172</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>4.553789934495394</v>
       </c>
       <c r="E41">
-        <v>-27.1460844268558</v>
+        <v>-25.10460305945793</v>
       </c>
       <c r="F41">
-        <v>6.726440082470606</v>
+        <v>6.253304786483223</v>
       </c>
       <c r="G41">
-        <v>-2.817404515864146</v>
+        <v>-2.789387368965293</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>4.482117249441683</v>
       </c>
       <c r="E42">
-        <v>-24.92829145244329</v>
+        <v>-25.38617904478087</v>
       </c>
       <c r="F42">
-        <v>6.499238784700368</v>
+        <v>6.701613911408704</v>
       </c>
       <c r="G42">
-        <v>-3.226770024522724</v>
+        <v>-1.936229988585255</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>4.403719984134308</v>
       </c>
       <c r="E43">
-        <v>-24.78452598812178</v>
+        <v>-25.71667160633466</v>
       </c>
       <c r="F43">
-        <v>6.942204939877793</v>
+        <v>6.327804837221399</v>
       </c>
       <c r="G43">
-        <v>-2.780869335292749</v>
+        <v>-2.142520012773861</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>4.31748724583594</v>
       </c>
       <c r="E44">
-        <v>-25.10100745109584</v>
+        <v>-24.54301794081871</v>
       </c>
       <c r="F44">
-        <v>6.54523968331263</v>
+        <v>6.251343212473394</v>
       </c>
       <c r="G44">
-        <v>-2.537762734161908</v>
+        <v>-2.18213400069678</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.221908734062388</v>
       </c>
       <c r="E45">
-        <v>-23.08647050404361</v>
+        <v>-24.36398472092547</v>
       </c>
       <c r="F45">
-        <v>6.479203890696259</v>
+        <v>6.181263330196556</v>
       </c>
       <c r="G45">
-        <v>-2.571672652120663</v>
+        <v>-1.984868523648228</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.118386140774864</v>
       </c>
       <c r="E46">
-        <v>-22.55670697225629</v>
+        <v>-23.05971627960629</v>
       </c>
       <c r="F46">
-        <v>6.53844872734448</v>
+        <v>6.144651147727623</v>
       </c>
       <c r="G46">
-        <v>-2.90419046717614</v>
+        <v>-2.897688555737011</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.007727391831097</v>
       </c>
       <c r="E47">
-        <v>-23.02337074722073</v>
+        <v>-22.24983493112651</v>
       </c>
       <c r="F47">
-        <v>6.560130415745355</v>
+        <v>6.345066357160936</v>
       </c>
       <c r="G47">
-        <v>-2.807714549070699</v>
+        <v>-2.555510568797941</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>3.889722652972055</v>
       </c>
       <c r="E48">
-        <v>-21.36341331496908</v>
+        <v>-23.13579011446114</v>
       </c>
       <c r="F48">
-        <v>6.569451205761654</v>
+        <v>6.157701247791326</v>
       </c>
       <c r="G48">
-        <v>-2.190413675090497</v>
+        <v>-2.133081647441398</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>3.763340935226059</v>
       </c>
       <c r="E49">
-        <v>-21.86288588411909</v>
+        <v>-22.37968892329646</v>
       </c>
       <c r="F49">
-        <v>6.317466812034461</v>
+        <v>6.341953352461215</v>
       </c>
       <c r="G49">
-        <v>-2.66812208586179</v>
+        <v>-2.858951862381999</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>3.62514309448317</v>
       </c>
       <c r="E50">
-        <v>-22.19015417217942</v>
+        <v>-21.42994112661577</v>
       </c>
       <c r="F50">
-        <v>6.639110277397871</v>
+        <v>6.349880828506006</v>
       </c>
       <c r="G50">
-        <v>-2.474127427806038</v>
+        <v>-3.029173492920245</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>3.47447845684557</v>
       </c>
       <c r="E51">
-        <v>-21.65301375623361</v>
+        <v>-21.59641688808575</v>
       </c>
       <c r="F51">
-        <v>6.395144480129777</v>
+        <v>6.162285432998419</v>
       </c>
       <c r="G51">
-        <v>-2.674633928937536</v>
+        <v>-2.692908140314314</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>3.309206431711193</v>
       </c>
       <c r="E52">
-        <v>-20.07923318434793</v>
+        <v>-20.3885777722859</v>
       </c>
       <c r="F52">
-        <v>6.703648381749979</v>
+        <v>6.341681647953097</v>
       </c>
       <c r="G52">
-        <v>-2.678924395956432</v>
+        <v>-3.149501891636135</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.127030580181557</v>
       </c>
       <c r="E53">
-        <v>-19.73569408917804</v>
+        <v>-20.12811806126073</v>
       </c>
       <c r="F53">
-        <v>6.382260053546633</v>
+        <v>6.428524372992985</v>
       </c>
       <c r="G53">
-        <v>-2.588092957995448</v>
+        <v>-3.873038171971549</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>2.925726461375892</v>
       </c>
       <c r="E54">
-        <v>-20.93070856658816</v>
+        <v>-19.59580499860709</v>
       </c>
       <c r="F54">
-        <v>6.165091941759104</v>
+        <v>6.258997327275261</v>
       </c>
       <c r="G54">
-        <v>-2.998819100870667</v>
+        <v>-3.294156178974589</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.703152760598905</v>
       </c>
       <c r="E55">
-        <v>-20.58186209988128</v>
+        <v>-19.26673890636572</v>
       </c>
       <c r="F55">
-        <v>6.352200257233845</v>
+        <v>6.220678707956561</v>
       </c>
       <c r="G55">
-        <v>-3.476825460740495</v>
+        <v>-3.717250519984526</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.459423855407004</v>
       </c>
       <c r="E56">
-        <v>-18.75266200854097</v>
+        <v>-18.90369114517079</v>
       </c>
       <c r="F56">
-        <v>5.968165815826382</v>
+        <v>6.824929653193855</v>
       </c>
       <c r="G56">
-        <v>-3.496443753606216</v>
+        <v>-3.238115264085807</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.196654434552414</v>
       </c>
       <c r="E57">
-        <v>-18.45154565787494</v>
+        <v>-18.51289742373086</v>
       </c>
       <c r="F57">
-        <v>6.126978757556298</v>
+        <v>6.03392824719983</v>
       </c>
       <c r="G57">
-        <v>-3.678152977165733</v>
+        <v>-3.616639730500535</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.916344482691045</v>
       </c>
       <c r="E58">
-        <v>-19.79243586849415</v>
+        <v>-18.40282833450042</v>
       </c>
       <c r="F58">
-        <v>6.20469950075656</v>
+        <v>6.127613286986842</v>
       </c>
       <c r="G58">
-        <v>-3.736925092124414</v>
+        <v>-4.216305328393039</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.620922318209559</v>
       </c>
       <c r="E59">
-        <v>-18.62602776139048</v>
+        <v>-17.51716297350228</v>
       </c>
       <c r="F59">
-        <v>5.970263242090271</v>
+        <v>6.283492151376042</v>
       </c>
       <c r="G59">
-        <v>-3.43855555430652</v>
+        <v>-3.997081002782501</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.313731504373803</v>
       </c>
       <c r="E60">
-        <v>-18.27779263867464</v>
+        <v>-17.95962658336973</v>
       </c>
       <c r="F60">
-        <v>6.304300740534366</v>
+        <v>6.151688957181808</v>
       </c>
       <c r="G60">
-        <v>-3.877778873183785</v>
+        <v>-4.627124166543358</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.9986271298559274</v>
       </c>
       <c r="E61">
-        <v>-18.2156031051273</v>
+        <v>-18.495861304514</v>
       </c>
       <c r="F61">
-        <v>6.055064869849662</v>
+        <v>5.990226896497739</v>
       </c>
       <c r="G61">
-        <v>-4.60458266196646</v>
+        <v>-4.287273493118396</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.6834086815939703</v>
       </c>
       <c r="E62">
-        <v>-19.38925677064324</v>
+        <v>-18.40542315010682</v>
       </c>
       <c r="F62">
-        <v>5.806428737164585</v>
+        <v>5.954926847994841</v>
       </c>
       <c r="G62">
-        <v>-5.116055326692781</v>
+        <v>-4.052827279118289</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.3731292977234702</v>
       </c>
       <c r="E63">
-        <v>-18.08277390553431</v>
+        <v>-16.36272362320088</v>
       </c>
       <c r="F63">
-        <v>6.402505352871053</v>
+        <v>6.22183510885087</v>
       </c>
       <c r="G63">
-        <v>-4.324255597337594</v>
+        <v>-4.592042315463701</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.07354462421522059</v>
       </c>
       <c r="E64">
-        <v>-16.92393740697147</v>
+        <v>-17.5896728993131</v>
       </c>
       <c r="F64">
-        <v>5.73681439736812</v>
+        <v>5.855014142073581</v>
       </c>
       <c r="G64">
-        <v>-4.321143684530679</v>
+        <v>-5.028531123725529</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.2097304111434835</v>
       </c>
       <c r="E65">
-        <v>-17.13334763050817</v>
+        <v>-16.37583355545309</v>
       </c>
       <c r="F65">
-        <v>5.600718603292578</v>
+        <v>6.178476702253538</v>
       </c>
       <c r="G65">
-        <v>-4.612071115976292</v>
+        <v>-4.76865329889274</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.4723014427029126</v>
       </c>
       <c r="E66">
-        <v>-16.91547821752514</v>
+        <v>-18.26594615067057</v>
       </c>
       <c r="F66">
-        <v>5.855043963300083</v>
+        <v>6.068351882990566</v>
       </c>
       <c r="G66">
-        <v>-4.369768977411495</v>
+        <v>-4.290454927381635</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.7077543698304936</v>
       </c>
       <c r="E67">
-        <v>-16.4852414874784</v>
+        <v>-16.6182563545057</v>
       </c>
       <c r="F67">
-        <v>5.422627895364712</v>
+        <v>6.021597170041757</v>
       </c>
       <c r="G67">
-        <v>-4.276593673208707</v>
+        <v>-4.428269627635956</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.9120405422482015</v>
       </c>
       <c r="E68">
-        <v>-16.99600807080354</v>
+        <v>-16.09560252691043</v>
       </c>
       <c r="F68">
-        <v>5.691790972291161</v>
+        <v>5.979198012896867</v>
       </c>
       <c r="G68">
-        <v>-4.669423006898626</v>
+        <v>-4.419933673968071</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.082034510653646</v>
       </c>
       <c r="E69">
-        <v>-16.70248144257437</v>
+        <v>-16.56482036121519</v>
       </c>
       <c r="F69">
-        <v>5.235618983978307</v>
+        <v>5.836645923283905</v>
       </c>
       <c r="G69">
-        <v>-3.686465757014843</v>
+        <v>-5.344721328181319</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.214838498901507</v>
       </c>
       <c r="E70">
-        <v>-16.26546558693815</v>
+        <v>-16.28568522338239</v>
       </c>
       <c r="F70">
-        <v>5.74888702389652</v>
+        <v>5.4223578475914</v>
       </c>
       <c r="G70">
-        <v>-4.337024371482563</v>
+        <v>-4.929694786650587</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.307740679571348</v>
       </c>
       <c r="E71">
-        <v>-17.3185712743699</v>
+        <v>-17.50919738772279</v>
       </c>
       <c r="F71">
-        <v>5.236473859137996</v>
+        <v>5.624794273487542</v>
       </c>
       <c r="G71">
-        <v>-4.403351151361862</v>
+        <v>-4.715297236436307</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.357678035673159</v>
       </c>
       <c r="E72">
-        <v>-15.47484383841299</v>
+        <v>-18.14544345732646</v>
       </c>
       <c r="F72">
-        <v>5.422490386375848</v>
+        <v>5.472982693046089</v>
       </c>
       <c r="G72">
-        <v>-4.077639817935126</v>
+        <v>-5.54027194264053</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.362115060838994</v>
       </c>
       <c r="E73">
-        <v>-16.6489503513297</v>
+        <v>-17.7972536193507</v>
       </c>
       <c r="F73">
-        <v>5.100447647924289</v>
+        <v>5.441213146413922</v>
       </c>
       <c r="G73">
-        <v>-4.481913707554305</v>
+        <v>-4.057683849424399</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.31864516765816</v>
       </c>
       <c r="E74">
-        <v>-17.01893573470438</v>
+        <v>-17.82048921948405</v>
       </c>
       <c r="F74">
-        <v>5.037581188991029</v>
+        <v>5.684600743234862</v>
       </c>
       <c r="G74">
-        <v>-4.094487184184477</v>
+        <v>-3.749879256819582</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.225194814374853</v>
       </c>
       <c r="E75">
-        <v>-16.76175463886076</v>
+        <v>-19.26912088369376</v>
       </c>
       <c r="F75">
-        <v>5.024047322364091</v>
+        <v>5.521263258750855</v>
       </c>
       <c r="G75">
-        <v>-3.911195519857189</v>
+        <v>-4.344036106934739</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.080721002027565</v>
       </c>
       <c r="E76">
-        <v>-17.26571945422638</v>
+        <v>-17.94336030473417</v>
       </c>
       <c r="F76">
-        <v>5.014189750270777</v>
+        <v>5.279542337144348</v>
       </c>
       <c r="G76">
-        <v>-3.549154259682492</v>
+        <v>-3.683982847860389</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.8857248536538486</v>
       </c>
       <c r="E77">
-        <v>-16.49437541955188</v>
+        <v>-19.9276017606751</v>
       </c>
       <c r="F77">
-        <v>5.117936140532192</v>
+        <v>5.502871845673901</v>
       </c>
       <c r="G77">
-        <v>-4.446951036114063</v>
+        <v>-3.153772495381795</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.6448956051994384</v>
       </c>
       <c r="E78">
-        <v>-18.66519906155683</v>
+        <v>-18.45397291994305</v>
       </c>
       <c r="F78">
-        <v>5.316161146552503</v>
+        <v>5.111133587420403</v>
       </c>
       <c r="G78">
-        <v>-3.392009284024367</v>
+        <v>-4.560383568471651</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.3624621171009024</v>
       </c>
       <c r="E79">
-        <v>-18.15944097048417</v>
+        <v>-19.5190564211251</v>
       </c>
       <c r="F79">
-        <v>4.864174070358592</v>
+        <v>5.700758877793869</v>
       </c>
       <c r="G79">
-        <v>-3.271389557301021</v>
+        <v>-3.085164749625938</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.04429516852507662</v>
       </c>
       <c r="E80">
-        <v>-19.5032928031044</v>
+        <v>-19.93980146965176</v>
       </c>
       <c r="F80">
-        <v>4.9445422757782</v>
+        <v>5.193175094993666</v>
       </c>
       <c r="G80">
-        <v>-3.510040164136003</v>
+        <v>-3.513363951857431</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.3027363111095846</v>
       </c>
       <c r="E81">
-        <v>-20.11103212882979</v>
+        <v>-20.45716603960607</v>
       </c>
       <c r="F81">
-        <v>4.409377171934385</v>
+        <v>5.298656086596544</v>
       </c>
       <c r="G81">
-        <v>-2.863166186853491</v>
+        <v>-3.088551437712613</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.671816670111579</v>
       </c>
       <c r="E82">
-        <v>-21.18127356190657</v>
+        <v>-21.01160522626119</v>
       </c>
       <c r="F82">
-        <v>4.685672492198938</v>
+        <v>4.931753939813781</v>
       </c>
       <c r="G82">
-        <v>-2.800444591066459</v>
+        <v>-3.112622414328654</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.053025191780805</v>
       </c>
       <c r="E83">
-        <v>-21.26133245388818</v>
+        <v>-21.31663417846985</v>
       </c>
       <c r="F83">
-        <v>4.441201390815136</v>
+        <v>4.772652726227691</v>
       </c>
       <c r="G83">
-        <v>-2.323805486504351</v>
+        <v>-2.818036830062146</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.438671524013938</v>
       </c>
       <c r="E84">
-        <v>-22.85544587406829</v>
+        <v>-23.08590897326665</v>
       </c>
       <c r="F84">
-        <v>4.360886200909308</v>
+        <v>4.800013701542159</v>
       </c>
       <c r="G84">
-        <v>-2.04686179941662</v>
+        <v>-1.821678491835394</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.822950262605557</v>
       </c>
       <c r="E85">
-        <v>-23.80066972521532</v>
+        <v>-24.23398581758727</v>
       </c>
       <c r="F85">
-        <v>4.497860064431817</v>
+        <v>5.006191034629345</v>
       </c>
       <c r="G85">
-        <v>-1.518929102269044</v>
+        <v>-2.709917723295089</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.200419365741668</v>
       </c>
       <c r="E86">
-        <v>-24.40424285485366</v>
+        <v>-26.03827024493738</v>
       </c>
       <c r="F86">
-        <v>4.621048237636937</v>
+        <v>4.835426408011838</v>
       </c>
       <c r="G86">
-        <v>-0.9431590220789987</v>
+        <v>-1.536772942725715</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.566762649667406</v>
       </c>
       <c r="E87">
-        <v>-25.46337594118962</v>
+        <v>-27.10360734066386</v>
       </c>
       <c r="F87">
-        <v>4.139072604726878</v>
+        <v>4.404484834053451</v>
       </c>
       <c r="G87">
-        <v>-1.840323484312569</v>
+        <v>-1.995002103543937</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.916941425099989</v>
       </c>
       <c r="E88">
-        <v>-26.01566410269109</v>
+        <v>-27.14582630383737</v>
       </c>
       <c r="F88">
-        <v>4.018926196624838</v>
+        <v>4.421817593589628</v>
       </c>
       <c r="G88">
-        <v>-0.7816043997625648</v>
+        <v>-1.463517191032722</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.246075088326698</v>
       </c>
       <c r="E89">
-        <v>-28.57935550723149</v>
+        <v>-29.44290832965018</v>
       </c>
       <c r="F89">
-        <v>3.805056643835256</v>
+        <v>4.336159433935743</v>
       </c>
       <c r="G89">
-        <v>-1.763677733987362</v>
+        <v>-1.781912218817668</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.553162822705288</v>
       </c>
       <c r="E90">
-        <v>-30.46992774256075</v>
+        <v>-30.37979752438609</v>
       </c>
       <c r="F90">
-        <v>3.94549971004069</v>
+        <v>4.243380628087392</v>
       </c>
       <c r="G90">
-        <v>-0.6213342691153682</v>
+        <v>-1.179869649227967</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.83612725896405</v>
       </c>
       <c r="E91">
-        <v>-31.76381918569135</v>
+        <v>-32.14986253789723</v>
       </c>
       <c r="F91">
-        <v>3.979398160898051</v>
+        <v>4.065429085883197</v>
       </c>
       <c r="G91">
-        <v>-1.290133989504473</v>
+        <v>-1.759814327343033</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>4.092857281173539</v>
       </c>
       <c r="E92">
-        <v>-34.02032155592143</v>
+        <v>-34.92892816624244</v>
       </c>
       <c r="F92">
-        <v>3.847527040576787</v>
+        <v>4.128524174219629</v>
       </c>
       <c r="G92">
-        <v>-0.4252043091867859</v>
+        <v>-1.758668878586445</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.320843780007908</v>
       </c>
       <c r="E93">
-        <v>-35.65412478654178</v>
+        <v>-35.9585967364475</v>
       </c>
       <c r="F93">
-        <v>3.474509885626558</v>
+        <v>3.689966590359904</v>
       </c>
       <c r="G93">
-        <v>-1.382892164969312</v>
+        <v>-1.565329708547468</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.515105357794586</v>
       </c>
       <c r="E94">
-        <v>-37.22221080236281</v>
+        <v>-36.87540667743339</v>
       </c>
       <c r="F94">
-        <v>3.104968560298476</v>
+        <v>3.224995683494514</v>
       </c>
       <c r="G94">
-        <v>-1.09273278008881</v>
+        <v>-1.698281217404599</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.675857167639548</v>
       </c>
       <c r="E95">
-        <v>-39.06270264364125</v>
+        <v>-39.54854224179117</v>
       </c>
       <c r="F95">
-        <v>3.055718804732435</v>
+        <v>3.380084285381443</v>
       </c>
       <c r="G95">
-        <v>-1.426955526097011</v>
+        <v>-1.232351727662033</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.799218846323495</v>
       </c>
       <c r="E96">
-        <v>-41.42907258600842</v>
+        <v>-40.99882679901366</v>
       </c>
       <c r="F96">
-        <v>2.990385467673637</v>
+        <v>3.079330589181831</v>
       </c>
       <c r="G96">
-        <v>-0.502601553349407</v>
+        <v>-1.71349648470309</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>4.884651377474522</v>
       </c>
       <c r="E97">
-        <v>-43.65316693200261</v>
+        <v>-43.45299479544155</v>
       </c>
       <c r="F97">
-        <v>2.200164383773049</v>
+        <v>2.495366361639098</v>
       </c>
       <c r="G97">
-        <v>-2.641369567358939</v>
+        <v>-2.789648902062896</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.923634586490941</v>
       </c>
       <c r="E98">
-        <v>-45.18553687332514</v>
+        <v>-45.51240439143579</v>
       </c>
       <c r="F98">
-        <v>1.996455585546206</v>
+        <v>2.343732051821843</v>
       </c>
       <c r="G98">
-        <v>-1.481205435849049</v>
+        <v>-3.128996372565889</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>4.919162446845148</v>
       </c>
       <c r="E99">
-        <v>-48.22778835404813</v>
+        <v>-47.89270165561356</v>
       </c>
       <c r="F99">
-        <v>1.764492831944677</v>
+        <v>2.031048208287113</v>
       </c>
       <c r="G99">
-        <v>-2.957073121620458</v>
+        <v>-3.871972176307904</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>4.857716196217893</v>
       </c>
       <c r="E100">
-        <v>-50.45622324237866</v>
+        <v>-49.5377173878769</v>
       </c>
       <c r="F100">
-        <v>1.789693425072644</v>
+        <v>1.792345857496408</v>
       </c>
       <c r="G100">
-        <v>-1.863818426004777</v>
+        <v>-2.693368306144272</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>4.754353599593173</v>
       </c>
       <c r="E101">
-        <v>-51.66210492528869</v>
+        <v>-52.14709996303618</v>
       </c>
       <c r="F101">
-        <v>0.9786140499695638</v>
+        <v>1.275442941414711</v>
       </c>
       <c r="G101">
-        <v>-3.429180089339304</v>
+        <v>-2.797100940071795</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>4.578414160918437</v>
       </c>
       <c r="E102">
-        <v>-55.01642826742076</v>
+        <v>-54.03331241001456</v>
       </c>
       <c r="F102">
-        <v>0.8781397109492062</v>
+        <v>0.7036258934666287</v>
       </c>
       <c r="G102">
-        <v>-2.052201709371464</v>
+        <v>-3.653009383794968</v>
       </c>
     </row>
   </sheetData>
